--- a/tools/importer/reports/import-magazine.report.xlsx
+++ b/tools/importer/reports/import-magazine.report.xlsx
@@ -64,7 +64,7 @@
     <t>us/en/magazine.report.json</t>
   </si>
   <si>
-    <t>["columns-featured","cards-article","columns-imgbottom","columns-imgbottom"]</t>
+    <t>["columns-featured","cards-article","cards-member","cards-member"]</t>
   </si>
   <si>
     <t>us/en/magazine</t>
@@ -73,7 +73,7 @@
     <t>magazine</t>
   </si>
   <si>
-    <t>2026-08-10T16:44:37.079Z</t>
+    <t>2026-08-10T17:07:20.707Z</t>
   </si>
   <si>
     <t>Magazine</t>
